--- a/data/belgrad/rca_analysis.xlsx
+++ b/data/belgrad/rca_analysis.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3178,6 +3178,150 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-26 14:55</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>1531</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Pantograf</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Pantograf Motoru</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>servis_disi</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>motoru bozuk</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-27 15:25</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>1531</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Auxiliary_Power_Unit</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>DBS Şalteri</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>servis_disi</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-27 15:30</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>1531</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Auxiliary_Power_Unit</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>DBS Şalteri</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>servis_disi</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-27 15:30</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>1535</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Sanding_System</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Kumlama Kontrol ünitesi</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>servis_disi</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-27 15:50</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>1534</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>ESS_Battery_Box</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>ESS Batarya BMS Kartı</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>servis_disi</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
